--- a/artfynd/A 2242-2026 artfynd.xlsx
+++ b/artfynd/A 2242-2026 artfynd.xlsx
@@ -3710,7 +3710,7 @@
         <v>122630048</v>
       </c>
       <c r="B26" t="n">
-        <v>57693</v>
+        <v>57695</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>122629949</v>
       </c>
       <c r="B27" t="n">
-        <v>57693</v>
+        <v>57695</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 2242-2026 artfynd.xlsx
+++ b/artfynd/A 2242-2026 artfynd.xlsx
@@ -3710,7 +3710,7 @@
         <v>122630048</v>
       </c>
       <c r="B26" t="n">
-        <v>57695</v>
+        <v>57703</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>122629949</v>
       </c>
       <c r="B27" t="n">
-        <v>57695</v>
+        <v>57703</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
